--- a/academias/Humanidades - Estadisticos 20212.xlsx
+++ b/academias/Humanidades - Estadisticos 20212.xlsx
@@ -726,22 +726,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>22.86</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -863,22 +866,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>12.12</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1561,22 +1567,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>22.86</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1698,22 +1707,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>12.12</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Humanidades - Estadisticos 20212.xlsx
+++ b/academias/Humanidades - Estadisticos 20212.xlsx
@@ -516,25 +516,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>57.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>42.11</v>
+        <v>15.79</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>42.11</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -551,25 +551,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H3" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -586,25 +586,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H4" s="1">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -723,22 +723,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>77.14</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>22.86</v>
+        <v>17.65</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>18.18</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -953,22 +953,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -985,22 +988,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>9.68</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1017,22 +1023,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1049,22 +1058,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1081,22 +1093,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1142,13 +1157,13 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1157,7 +1172,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1357,25 +1372,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>57.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>42.11</v>
+        <v>15.79</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>42.11</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1392,25 +1407,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H3" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1427,25 +1442,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H4" s="1">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1462,19 +1477,19 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1497,16 +1512,16 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H6" s="1">
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="I6" s="2">
         <v>7.5</v>
@@ -1564,22 +1579,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>77.14</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>22.86</v>
+        <v>17.65</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1649,7 +1664,7 @@
         <v>18.18</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20212.xlsx
+++ b/academias/Humanidades - Estadisticos 20212.xlsx
@@ -988,25 +988,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>90.31999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H3" s="1">
-        <v>9.68</v>
+        <v>6.45</v>
       </c>
       <c r="I3" s="2">
         <v>8.4</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>9.68</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1128,22 +1128,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>71.05</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>28.95</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1160,22 +1163,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1192,22 +1198,25 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1224,22 +1233,25 @@
         <v>22</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1256,22 +1268,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>19.35</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1288,22 +1303,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>6.06</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.9</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1547,19 +1565,19 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>68.42</v>
+        <v>71.05</v>
       </c>
       <c r="H7" s="1">
-        <v>31.58</v>
+        <v>28.95</v>
       </c>
       <c r="I7" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1582,19 +1600,19 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H8" s="1">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1617,19 +1635,19 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H9" s="1">
-        <v>25</v>
+        <v>16.67</v>
       </c>
       <c r="I9" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1652,19 +1670,19 @@
         <v>22</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>81.81999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="H10" s="1">
-        <v>18.18</v>
+        <v>22.73</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1687,19 +1705,19 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>22.58</v>
+        <v>19.35</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1722,19 +1740,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="H12" s="1">
-        <v>12.12</v>
+        <v>6.06</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20212.xlsx
+++ b/academias/Humanidades - Estadisticos 20212.xlsx
@@ -516,25 +516,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H2" s="1">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
       <c r="I2" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -551,25 +551,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
         <v>7.5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -598,13 +598,13 @@
         <v>9.09</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -953,25 +953,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
       <c r="I2" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -988,25 +988,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>93.55</v>
+        <v>96.77</v>
       </c>
       <c r="H3" s="1">
-        <v>6.45</v>
+        <v>3.23</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1023,25 +1023,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H4" s="1">
-        <v>18.18</v>
+        <v>9.09</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1390,25 +1390,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>84.20999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H2" s="1">
-        <v>15.79</v>
+        <v>21.05</v>
       </c>
       <c r="I2" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1440,10 +1440,10 @@
         <v>8.1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1472,13 +1472,13 @@
         <v>9.09</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1530,16 +1530,16 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>87.5</v>
+        <v>81.25</v>
       </c>
       <c r="H6" s="1">
-        <v>12.5</v>
+        <v>18.75</v>
       </c>
       <c r="I6" s="2">
         <v>7.5</v>
@@ -1565,19 +1565,19 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>71.05</v>
+        <v>92.11</v>
       </c>
       <c r="H7" s="1">
-        <v>28.95</v>
+        <v>7.89</v>
       </c>
       <c r="I7" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1600,19 +1600,19 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1635,16 +1635,16 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H9" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="I9" s="2">
         <v>7.5</v>
@@ -1670,19 +1670,19 @@
         <v>22</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1705,19 +1705,19 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1740,19 +1740,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>0</v>
